--- a/合同全生命周期管理系统-项目管理套件/01_项目启动与治理/安全合规会签清单-20260924-V1.xlsx
+++ b/合同全生命周期管理系统-项目管理套件/01_项目启动与治理/安全合规会签清单-20260924-V1.xlsx
@@ -7,9 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会签项目" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会签结果" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'会签结果'!$A$4:$J$21</definedName>
